--- a/imports/EtatPaiement.xlsx
+++ b/imports/EtatPaiement.xlsx
@@ -10,6 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">A!$A$1:$M$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">A!$A$1:$M$233</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -21,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
-    <t>matricule</t>
+    <t>Matricule</t>
   </si>
   <si>
     <t>IDannee</t>
@@ -57,7 +58,7 @@
     <t>date_paie</t>
   </si>
   <si>
-    <t>id_etat_paie</t>
+    <t>IDEtat</t>
   </si>
   <si>
     <t>24527</t>
@@ -10819,134 +10820,134 @@
       </c>
     </row>
     <row r="234" ht="15" customHeight="1">
-      <c r="G234" s="5"/>
-      <c r="H234" s="5"/>
+      <c r="G234"/>
+      <c r="H234"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="G235" s="5"/>
-      <c r="H235" s="5"/>
+      <c r="G235"/>
+      <c r="H235"/>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="G236" s="5"/>
-      <c r="H236" s="5"/>
+      <c r="G236"/>
+      <c r="H236"/>
     </row>
     <row r="237" ht="15" customHeight="1">
-      <c r="G237" s="5"/>
-      <c r="H237" s="5"/>
+      <c r="G237"/>
+      <c r="H237"/>
     </row>
     <row r="238" ht="15" customHeight="1">
-      <c r="G238" s="5"/>
-      <c r="H238" s="5"/>
+      <c r="G238"/>
+      <c r="H238"/>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="G239" s="5"/>
-      <c r="H239" s="5"/>
+      <c r="G239"/>
+      <c r="H239"/>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="G240" s="5"/>
-      <c r="H240" s="5"/>
+      <c r="G240"/>
+      <c r="H240"/>
     </row>
     <row r="241" ht="15" customHeight="1">
-      <c r="G241" s="5"/>
-      <c r="H241" s="5"/>
+      <c r="G241"/>
+      <c r="H241"/>
     </row>
     <row r="242" ht="15" customHeight="1">
-      <c r="G242" s="5"/>
-      <c r="H242" s="5"/>
+      <c r="G242"/>
+      <c r="H242"/>
     </row>
     <row r="243" ht="15" customHeight="1">
-      <c r="G243" s="5"/>
-      <c r="H243" s="5"/>
+      <c r="G243"/>
+      <c r="H243"/>
     </row>
     <row r="244" ht="15" customHeight="1">
-      <c r="H244" s="5"/>
+      <c r="H244"/>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c r="H245" s="5"/>
+      <c r="H245"/>
     </row>
     <row r="246" ht="15" customHeight="1">
-      <c r="H246" s="5"/>
+      <c r="H246"/>
     </row>
     <row r="247" ht="15" customHeight="1">
-      <c r="H247" s="5"/>
+      <c r="H247"/>
     </row>
     <row r="248" ht="15" customHeight="1">
-      <c r="H248" s="5"/>
+      <c r="H248"/>
     </row>
     <row r="249" ht="15" customHeight="1">
-      <c r="H249" s="5"/>
+      <c r="H249"/>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c r="H250" s="5"/>
+      <c r="H250"/>
     </row>
     <row r="251" ht="15" customHeight="1">
-      <c r="H251" s="5"/>
+      <c r="H251"/>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="H252" s="5"/>
+      <c r="H252"/>
     </row>
     <row r="253" ht="15" customHeight="1">
-      <c r="H253" s="5"/>
+      <c r="H253"/>
     </row>
     <row r="254" ht="15" customHeight="1">
-      <c r="H254" s="5"/>
+      <c r="H254"/>
     </row>
     <row r="255" ht="15" customHeight="1">
-      <c r="H255" s="5"/>
+      <c r="H255"/>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="H256" s="5"/>
+      <c r="H256"/>
     </row>
     <row r="257" ht="15" customHeight="1">
-      <c r="H257" s="5"/>
+      <c r="H257"/>
     </row>
     <row r="258" ht="15" customHeight="1">
-      <c r="H258" s="5"/>
+      <c r="H258"/>
     </row>
     <row r="259" ht="15" customHeight="1">
-      <c r="H259" s="5"/>
+      <c r="H259"/>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c r="H260" s="5"/>
+      <c r="H260"/>
     </row>
     <row r="261" ht="15" customHeight="1">
-      <c r="H261" s="5"/>
+      <c r="H261"/>
     </row>
     <row r="262" ht="15" customHeight="1">
-      <c r="H262" s="5"/>
+      <c r="H262"/>
     </row>
     <row r="263" ht="15" customHeight="1">
-      <c r="H263" s="5"/>
+      <c r="H263"/>
     </row>
     <row r="264" ht="15" customHeight="1">
-      <c r="H264" s="5"/>
+      <c r="H264"/>
     </row>
     <row r="265" ht="15" customHeight="1">
-      <c r="H265" s="5"/>
+      <c r="H265"/>
     </row>
     <row r="266" ht="15" customHeight="1">
-      <c r="H266" s="5"/>
+      <c r="H266"/>
     </row>
     <row r="267" ht="15" customHeight="1">
-      <c r="H267" s="5"/>
+      <c r="H267"/>
     </row>
     <row r="268" ht="15" customHeight="1">
-      <c r="H268" s="5"/>
+      <c r="H268"/>
     </row>
     <row r="269" ht="15" customHeight="1">
-      <c r="H269" s="5"/>
+      <c r="H269"/>
     </row>
     <row r="270" ht="15" customHeight="1">
-      <c r="H270" s="5"/>
+      <c r="H270"/>
     </row>
     <row r="271" ht="15" customHeight="1">
-      <c r="H271" s="5"/>
+      <c r="H271"/>
     </row>
     <row r="272" ht="15" customHeight="1">
-      <c r="H272" s="5"/>
+      <c r="H272"/>
     </row>
     <row r="273" ht="15" customHeight="1">
-      <c r="H273" s="5"/>
+      <c r="H273"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M233"/>

--- a/imports/EtatPaiement.xlsx
+++ b/imports/EtatPaiement.xlsx
@@ -1307,7 +1307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
+    <row r="2" ht="13.5" hidden="1" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" ht="13.5" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
+    <row r="4" ht="13.5" hidden="1" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
+    <row r="5" ht="13.5" hidden="1" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
+    <row r="6" ht="13.5" hidden="1" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
+    <row r="7" ht="13.5" hidden="1" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
+    <row r="8" ht="13.5" hidden="1" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
+    <row r="9" ht="13.5" hidden="1" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1">
+    <row r="10" ht="13.5" hidden="1" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1">
+    <row r="11" ht="13.5" hidden="1" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1">
+    <row r="12" ht="13.5" hidden="1" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
+    <row r="13" ht="13.5" hidden="1" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
+    <row r="14" ht="13.5" hidden="1" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" ht="13.5" hidden="1" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
+    <row r="16" ht="13.5" hidden="1" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" ht="13.5" hidden="1" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1">
+    <row r="18" ht="13.5" hidden="1" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
+    <row r="19" ht="13.5" hidden="1" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
+    <row r="20" ht="13.5" hidden="1" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
+    <row r="21" ht="13.5" hidden="1" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
+    <row r="22" ht="13.5" hidden="1" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
+    <row r="23" ht="13.5" hidden="1" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" ht="13.5" hidden="1" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
+    <row r="25" ht="13.5" hidden="1" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
+    <row r="26" ht="13.5" hidden="1" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>37</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
+    <row r="27" ht="13.5" hidden="1" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" ht="13.5" hidden="1" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>39</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" ht="13.5" hidden="1" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
+    <row r="30" ht="13.5" hidden="1" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>41</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
+    <row r="31" ht="13.5" hidden="1" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>42</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
+    <row r="32" ht="13.5" hidden="1" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
+    <row r="33" ht="13.5" hidden="1" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>44</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1">
+    <row r="34" ht="13.5" hidden="1" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>45</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1">
+    <row r="35" ht="13.5" hidden="1" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
+    <row r="36" ht="13.5" hidden="1" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>47</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="37" ht="13.5" customHeight="1">
+    <row r="37" ht="13.5" hidden="1" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>48</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="38" ht="13.5" customHeight="1">
+    <row r="38" ht="13.5" hidden="1" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>49</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
+    <row r="39" ht="13.5" hidden="1" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>50</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
+    <row r="40" ht="13.5" hidden="1" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>51</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="41" ht="13.5" hidden="1" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>52</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
+    <row r="42" ht="13.5" hidden="1" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>53</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="43" ht="13.5" hidden="1" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>54</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="44" ht="13.5" customHeight="1">
+    <row r="44" ht="13.5" hidden="1" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>55</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="45" ht="13.5" customHeight="1">
+    <row r="45" ht="13.5" hidden="1" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>56</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="46" ht="13.5" customHeight="1">
+    <row r="46" ht="13.5" hidden="1" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>57</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="47" ht="13.5" hidden="1" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>58</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="48" ht="13.5" customHeight="1">
+    <row r="48" ht="13.5" hidden="1" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>59</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
+    <row r="49" ht="13.5" hidden="1" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>60</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1">
+    <row r="50" ht="13.5" hidden="1" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>61</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
+    <row r="51" ht="13.5" hidden="1" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>62</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" ht="13.5" hidden="1" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>63</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="53" ht="13.5" customHeight="1">
+    <row r="53" ht="13.5" hidden="1" customHeight="1">
       <c r="A53" s="3" t="s">
         <v>64</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="54" ht="13.5" customHeight="1">
+    <row r="54" ht="13.5" hidden="1" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>65</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="55" ht="13.5" hidden="1" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>66</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="56" ht="13.5" customHeight="1">
+    <row r="56" ht="13.5" hidden="1" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>67</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
+    <row r="57" ht="13.5" hidden="1" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>68</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
+    <row r="58" ht="13.5" hidden="1" customHeight="1">
       <c r="A58" s="3" t="s">
         <v>69</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="59" ht="13.5" customHeight="1">
+    <row r="59" ht="13.5" hidden="1" customHeight="1">
       <c r="A59" s="3" t="s">
         <v>70</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="60" ht="13.5" customHeight="1">
+    <row r="60" ht="13.5" hidden="1" customHeight="1">
       <c r="A60" s="3" t="s">
         <v>71</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="61" ht="13.5" hidden="1" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>72</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="62" ht="13.5" customHeight="1">
+    <row r="62" ht="13.5" hidden="1" customHeight="1">
       <c r="A62" s="3" t="s">
         <v>73</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
+    <row r="63" ht="13.5" hidden="1" customHeight="1">
       <c r="A63" s="3" t="s">
         <v>74</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
+    <row r="64" ht="13.5" hidden="1" customHeight="1">
       <c r="A64" s="3" t="s">
         <v>75</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="65" ht="13.5" customHeight="1">
+    <row r="65" ht="13.5" hidden="1" customHeight="1">
       <c r="A65" s="3" t="s">
         <v>76</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="66" ht="13.5" customHeight="1">
+    <row r="66" ht="13.5" hidden="1" customHeight="1">
       <c r="A66" s="3" t="s">
         <v>77</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
+    <row r="67" ht="13.5" hidden="1" customHeight="1">
       <c r="A67" s="3" t="s">
         <v>78</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="68" ht="13.5" customHeight="1">
+    <row r="68" ht="13.5" hidden="1" customHeight="1">
       <c r="A68" s="3" t="s">
         <v>79</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
+    <row r="69" ht="13.5" hidden="1" customHeight="1">
       <c r="A69" s="3" t="s">
         <v>80</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="70" ht="13.5" customHeight="1">
+    <row r="70" ht="13.5" hidden="1" customHeight="1">
       <c r="A70" s="3" t="s">
         <v>81</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="71" ht="13.5" customHeight="1">
+    <row r="71" ht="13.5" hidden="1" customHeight="1">
       <c r="A71" s="3" t="s">
         <v>82</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="72" ht="13.5" customHeight="1">
+    <row r="72" ht="13.5" hidden="1" customHeight="1">
       <c r="A72" s="3" t="s">
         <v>83</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
+    <row r="73" ht="13.5" hidden="1" customHeight="1">
       <c r="A73" s="3" t="s">
         <v>84</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="74" ht="13.5" customHeight="1">
+    <row r="74" ht="13.5" hidden="1" customHeight="1">
       <c r="A74" s="3" t="s">
         <v>85</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="75" ht="13.5" customHeight="1">
+    <row r="75" ht="13.5" hidden="1" customHeight="1">
       <c r="A75" s="3" t="s">
         <v>86</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="76" ht="13.5" customHeight="1">
+    <row r="76" ht="13.5" hidden="1" customHeight="1">
       <c r="A76" s="3" t="s">
         <v>87</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="77" ht="13.5" customHeight="1">
+    <row r="77" ht="13.5" hidden="1" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>88</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="78" ht="13.5" customHeight="1">
+    <row r="78" ht="13.5" hidden="1" customHeight="1">
       <c r="A78" s="3" t="s">
         <v>89</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="79" ht="13.5" customHeight="1">
+    <row r="79" ht="13.5" hidden="1" customHeight="1">
       <c r="A79" s="3" t="s">
         <v>90</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
+    <row r="80" ht="13.5" hidden="1" customHeight="1">
       <c r="A80" s="3" t="s">
         <v>91</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="81" ht="13.5" customHeight="1">
+    <row r="81" ht="13.5" hidden="1" customHeight="1">
       <c r="A81" s="3" t="s">
         <v>92</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
+    <row r="82" ht="13.5" hidden="1" customHeight="1">
       <c r="A82" s="3" t="s">
         <v>93</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="83" ht="13.5" customHeight="1">
+    <row r="83" ht="13.5" hidden="1" customHeight="1">
       <c r="A83" s="3" t="s">
         <v>94</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="84" ht="13.5" customHeight="1">
+    <row r="84" ht="13.5" hidden="1" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>95</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="85" ht="13.5" customHeight="1">
+    <row r="85" ht="13.5" hidden="1" customHeight="1">
       <c r="A85" s="3" t="s">
         <v>96</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" ht="13.5" hidden="1" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>76</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
+    <row r="87" ht="13.5" hidden="1" customHeight="1">
       <c r="A87" s="3" t="s">
         <v>97</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="88" ht="13.5" customHeight="1">
+    <row r="88" ht="13.5" hidden="1" customHeight="1">
       <c r="A88" s="3" t="s">
         <v>98</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="89" ht="13.5" customHeight="1">
+    <row r="89" ht="13.5" hidden="1" customHeight="1">
       <c r="A89" s="3" t="s">
         <v>99</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="90" ht="13.5" customHeight="1">
+    <row r="90" ht="13.5" hidden="1" customHeight="1">
       <c r="A90" s="3" t="s">
         <v>100</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="91" ht="13.5" customHeight="1">
+    <row r="91" ht="13.5" hidden="1" customHeight="1">
       <c r="A91" s="3" t="s">
         <v>101</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="92" ht="13.5" customHeight="1">
+    <row r="92" ht="13.5" hidden="1" customHeight="1">
       <c r="A92" s="3" t="s">
         <v>102</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="93" ht="13.5" customHeight="1">
+    <row r="93" ht="13.5" hidden="1" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>103</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" ht="13.5" hidden="1" customHeight="1">
       <c r="A94" s="3" t="s">
         <v>104</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="95" ht="13.5" customHeight="1">
+    <row r="95" ht="13.5" hidden="1" customHeight="1">
       <c r="A95" s="3" t="s">
         <v>105</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="96" ht="13.5" customHeight="1">
+    <row r="96" ht="13.5" hidden="1" customHeight="1">
       <c r="A96" s="3" t="s">
         <v>106</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="97" ht="13.5" customHeight="1">
+    <row r="97" ht="13.5" hidden="1" customHeight="1">
       <c r="A97" s="3" t="s">
         <v>107</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" ht="13.5" hidden="1" customHeight="1">
       <c r="A98" s="3" t="s">
         <v>108</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
+    <row r="99" ht="13.5" hidden="1" customHeight="1">
       <c r="A99" s="3" t="s">
         <v>109</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
+    <row r="100" ht="13.5" hidden="1" customHeight="1">
       <c r="A100" s="3" t="s">
         <v>110</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" ht="13.5" hidden="1" customHeight="1">
       <c r="A101" s="3" t="s">
         <v>111</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
+    <row r="102" ht="13.5" hidden="1" customHeight="1">
       <c r="A102" s="3" t="s">
         <v>112</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
+    <row r="103" ht="13.5" hidden="1" customHeight="1">
       <c r="A103" s="3" t="s">
         <v>113</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" ht="13.5" hidden="1" customHeight="1">
       <c r="A104" s="3" t="s">
         <v>114</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" ht="13.5" hidden="1" customHeight="1">
       <c r="A105" s="3" t="s">
         <v>115</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" ht="13.5" hidden="1" customHeight="1">
       <c r="A106" s="3" t="s">
         <v>116</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" ht="13.5" hidden="1" customHeight="1">
       <c r="A107" s="3" t="s">
         <v>117</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
+    <row r="108" ht="13.5" hidden="1" customHeight="1">
       <c r="A108" s="3" t="s">
         <v>118</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
+    <row r="109" ht="13.5" hidden="1" customHeight="1">
       <c r="A109" s="3" t="s">
         <v>119</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="110" ht="13.5" hidden="1" customHeight="1">
       <c r="A110" s="3" t="s">
         <v>120</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" ht="13.5" hidden="1" customHeight="1">
       <c r="A111" s="3" t="s">
         <v>121</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
+    <row r="112" ht="13.5" hidden="1" customHeight="1">
       <c r="A112" s="3" t="s">
         <v>122</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
+    <row r="113" ht="13.5" hidden="1" customHeight="1">
       <c r="A113" s="3" t="s">
         <v>123</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="114" ht="13.5" customHeight="1">
+    <row r="114" ht="13.5" hidden="1" customHeight="1">
       <c r="A114" s="3" t="s">
         <v>124</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="115" ht="13.5" customHeight="1">
+    <row r="115" ht="13.5" hidden="1" customHeight="1">
       <c r="A115" s="3" t="s">
         <v>125</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="116" ht="13.5" customHeight="1">
+    <row r="116" ht="13.5" hidden="1" customHeight="1">
       <c r="A116" s="3" t="s">
         <v>13</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
+    <row r="117" ht="13.5" hidden="1" customHeight="1">
       <c r="A117" s="3" t="s">
         <v>126</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="118" ht="13.5" customHeight="1">
+    <row r="118" ht="13.5" hidden="1" customHeight="1">
       <c r="A118" s="3" t="s">
         <v>127</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="119" ht="13.5" customHeight="1">
+    <row r="119" ht="13.5" hidden="1" customHeight="1">
       <c r="A119" s="3" t="s">
         <v>128</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" ht="13.5" hidden="1" customHeight="1">
       <c r="A120" s="3" t="s">
         <v>129</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" ht="13.5" hidden="1" customHeight="1">
       <c r="A121" s="3" t="s">
         <v>130</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
+    <row r="122" ht="13.5" hidden="1" customHeight="1">
       <c r="A122" s="3" t="s">
         <v>131</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="123" ht="13.5" customHeight="1">
+    <row r="123" ht="13.5" hidden="1" customHeight="1">
       <c r="A123" s="3" t="s">
         <v>132</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="124" ht="13.5" customHeight="1">
+    <row r="124" ht="13.5" hidden="1" customHeight="1">
       <c r="A124" s="3" t="s">
         <v>133</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" ht="13.5" hidden="1" customHeight="1">
       <c r="A125" s="3" t="s">
         <v>134</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="126" ht="13.5" customHeight="1">
+    <row r="126" ht="13.5" hidden="1" customHeight="1">
       <c r="A126" s="3" t="s">
         <v>135</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="127" ht="13.5" customHeight="1">
+    <row r="127" ht="13.5" hidden="1" customHeight="1">
       <c r="A127" s="3" t="s">
         <v>136</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="128" ht="13.5" customHeight="1">
+    <row r="128" ht="13.5" hidden="1" customHeight="1">
       <c r="A128" s="3" t="s">
         <v>137</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" ht="13.5" hidden="1" customHeight="1">
       <c r="A129" s="3" t="s">
         <v>138</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="130" ht="13.5" customHeight="1">
+    <row r="130" ht="13.5" hidden="1" customHeight="1">
       <c r="A130" s="3" t="s">
         <v>139</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="131" ht="13.5" customHeight="1">
+    <row r="131" ht="13.5" hidden="1" customHeight="1">
       <c r="A131" s="3" t="s">
         <v>140</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
+    <row r="132" ht="13.5" hidden="1" customHeight="1">
       <c r="A132" s="3" t="s">
         <v>141</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" ht="13.5" hidden="1" customHeight="1">
       <c r="A133" s="3" t="s">
         <v>142</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
+    <row r="134" ht="13.5" hidden="1" customHeight="1">
       <c r="A134" s="3" t="s">
         <v>143</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" ht="13.5" hidden="1" customHeight="1">
       <c r="A135" s="3" t="s">
         <v>144</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="136" ht="13.5" hidden="1" customHeight="1">
       <c r="A136" s="3" t="s">
         <v>145</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" ht="13.5" hidden="1" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>146</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="138" ht="13.5" hidden="1" customHeight="1">
       <c r="A138" s="3" t="s">
         <v>147</v>
       </c>
@@ -6924,7 +6924,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" ht="13.5" hidden="1" customHeight="1">
       <c r="A139" s="3" t="s">
         <v>148</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="140" ht="13.5" customHeight="1">
+    <row r="140" ht="13.5" hidden="1" customHeight="1">
       <c r="A140" s="3" t="s">
         <v>149</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="141" ht="13.5" customHeight="1">
+    <row r="141" ht="13.5" hidden="1" customHeight="1">
       <c r="A141" s="3" t="s">
         <v>150</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="142" ht="13.5" customHeight="1">
+    <row r="142" ht="13.5" hidden="1" customHeight="1">
       <c r="A142" s="3" t="s">
         <v>151</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="143" ht="13.5" customHeight="1">
+    <row r="143" ht="13.5" hidden="1" customHeight="1">
       <c r="A143" s="3" t="s">
         <v>152</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="144" ht="13.5" customHeight="1">
+    <row r="144" ht="13.5" hidden="1" customHeight="1">
       <c r="A144" s="3" t="s">
         <v>153</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="145" ht="13.5" customHeight="1">
+    <row r="145" ht="13.5" hidden="1" customHeight="1">
       <c r="A145" s="3" t="s">
         <v>154</v>
       </c>
@@ -7211,7 +7211,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="146" ht="13.5" customHeight="1">
+    <row r="146" ht="13.5" hidden="1" customHeight="1">
       <c r="A146" s="3" t="s">
         <v>155</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="147" ht="13.5" customHeight="1">
+    <row r="147" ht="13.5" hidden="1" customHeight="1">
       <c r="A147" s="3" t="s">
         <v>156</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="148" ht="13.5" customHeight="1">
+    <row r="148" ht="13.5" hidden="1" customHeight="1">
       <c r="A148" s="3" t="s">
         <v>157</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="149" ht="13.5" customHeight="1">
+    <row r="149" ht="13.5" hidden="1" customHeight="1">
       <c r="A149" s="3" t="s">
         <v>158</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="150" ht="13.5" customHeight="1">
+    <row r="150" ht="13.5" hidden="1" customHeight="1">
       <c r="A150" s="3" t="s">
         <v>159</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="151" ht="13.5" customHeight="1">
+    <row r="151" ht="13.5" hidden="1" customHeight="1">
       <c r="A151" s="3" t="s">
         <v>160</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="152" ht="13.5" customHeight="1">
+    <row r="152" ht="13.5" hidden="1" customHeight="1">
       <c r="A152" s="3" t="s">
         <v>161</v>
       </c>
@@ -7498,7 +7498,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="153" ht="13.5" customHeight="1">
+    <row r="153" ht="13.5" hidden="1" customHeight="1">
       <c r="A153" s="3" t="s">
         <v>162</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="154" ht="13.5" customHeight="1">
+    <row r="154" ht="13.5" hidden="1" customHeight="1">
       <c r="A154" s="3" t="s">
         <v>163</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="155" ht="13.5" customHeight="1">
+    <row r="155" ht="13.5" hidden="1" customHeight="1">
       <c r="A155" s="3" t="s">
         <v>164</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="156" ht="13.5" customHeight="1">
+    <row r="156" ht="13.5" hidden="1" customHeight="1">
       <c r="A156" s="3" t="s">
         <v>165</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="157" ht="13.5" customHeight="1">
+    <row r="157" ht="13.5" hidden="1" customHeight="1">
       <c r="A157" s="3" t="s">
         <v>166</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="158" ht="13.5" customHeight="1">
+    <row r="158" ht="13.5" hidden="1" customHeight="1">
       <c r="A158" s="3" t="s">
         <v>167</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="159" ht="13.5" customHeight="1">
+    <row r="159" ht="13.5" hidden="1" customHeight="1">
       <c r="A159" s="3" t="s">
         <v>168</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="160" ht="13.5" customHeight="1">
+    <row r="160" ht="13.5" hidden="1" customHeight="1">
       <c r="A160" s="3" t="s">
         <v>169</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="161" ht="13.5" customHeight="1">
+    <row r="161" ht="13.5" hidden="1" customHeight="1">
       <c r="A161" s="3" t="s">
         <v>170</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="162" ht="13.5" customHeight="1">
+    <row r="162" ht="13.5" hidden="1" customHeight="1">
       <c r="A162" s="3" t="s">
         <v>171</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="163" ht="13.5" customHeight="1">
+    <row r="163" ht="13.5" hidden="1" customHeight="1">
       <c r="A163" s="3" t="s">
         <v>172</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="164" ht="13.5" customHeight="1">
+    <row r="164" ht="13.5" hidden="1" customHeight="1">
       <c r="A164" s="3" t="s">
         <v>172</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="165" ht="13.5" customHeight="1">
+    <row r="165" ht="13.5" hidden="1" customHeight="1">
       <c r="A165" s="3" t="s">
         <v>173</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="166" ht="13.5" customHeight="1">
+    <row r="166" ht="13.5" hidden="1" customHeight="1">
       <c r="A166" s="3" t="s">
         <v>174</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="167" ht="13.5" customHeight="1">
+    <row r="167" ht="13.5" hidden="1" customHeight="1">
       <c r="A167" s="3" t="s">
         <v>175</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="168" ht="13.5" customHeight="1">
+    <row r="168" ht="13.5" hidden="1" customHeight="1">
       <c r="A168" s="3" t="s">
         <v>176</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="169" ht="13.5" customHeight="1">
+    <row r="169" ht="13.5" hidden="1" customHeight="1">
       <c r="A169" s="3" t="s">
         <v>177</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="170" ht="13.5" customHeight="1">
+    <row r="170" ht="13.5" hidden="1" customHeight="1">
       <c r="A170" s="3" t="s">
         <v>178</v>
       </c>
@@ -8236,7 +8236,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="171" ht="13.5" customHeight="1">
+    <row r="171" ht="13.5" hidden="1" customHeight="1">
       <c r="A171" s="3" t="s">
         <v>179</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="172" ht="13.5" customHeight="1">
+    <row r="172" ht="13.5" hidden="1" customHeight="1">
       <c r="A172" s="3" t="s">
         <v>180</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="173" ht="13.5" customHeight="1">
+    <row r="173" ht="13.5" hidden="1" customHeight="1">
       <c r="A173" s="3" t="s">
         <v>181</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="174" ht="13.5" customHeight="1">
+    <row r="174" ht="13.5" hidden="1" customHeight="1">
       <c r="A174" s="3" t="s">
         <v>182</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="175" ht="13.5" customHeight="1">
+    <row r="175" ht="13.5" hidden="1" customHeight="1">
       <c r="A175" s="3" t="s">
         <v>183</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="176" ht="13.5" customHeight="1">
+    <row r="176" ht="13.5" hidden="1" customHeight="1">
       <c r="A176" s="3" t="s">
         <v>184</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="177" ht="13.5" customHeight="1">
+    <row r="177" ht="13.5" hidden="1" customHeight="1">
       <c r="A177" s="3" t="s">
         <v>184</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="178" ht="13.5" customHeight="1">
+    <row r="178" ht="13.5" hidden="1" customHeight="1">
       <c r="A178" s="3" t="s">
         <v>185</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="179" ht="13.5" customHeight="1">
+    <row r="179" ht="13.5" hidden="1" customHeight="1">
       <c r="A179" s="3" t="s">
         <v>185</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="180" ht="13.5" customHeight="1">
+    <row r="180" ht="13.5" hidden="1" customHeight="1">
       <c r="A180" s="3" t="s">
         <v>186</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="181" ht="13.5" customHeight="1">
+    <row r="181" ht="13.5" hidden="1" customHeight="1">
       <c r="A181" s="3" t="s">
         <v>186</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="182" ht="13.5" customHeight="1">
+    <row r="182" ht="13.5" hidden="1" customHeight="1">
       <c r="A182" s="3" t="s">
         <v>187</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="183" ht="13.5" customHeight="1">
+    <row r="183" ht="13.5" hidden="1" customHeight="1">
       <c r="A183" s="3" t="s">
         <v>188</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="184" ht="13.5" customHeight="1">
+    <row r="184" ht="13.5" hidden="1" customHeight="1">
       <c r="A184" s="3" t="s">
         <v>189</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="185" ht="13.5" customHeight="1">
+    <row r="185" ht="13.5" hidden="1" customHeight="1">
       <c r="A185" s="3" t="s">
         <v>190</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="186" ht="13.5" customHeight="1">
+    <row r="186" ht="13.5" hidden="1" customHeight="1">
       <c r="A186" s="3" t="s">
         <v>191</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="187" ht="13.5" customHeight="1">
+    <row r="187" ht="13.5" hidden="1" customHeight="1">
       <c r="A187" s="3" t="s">
         <v>192</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="188" ht="13.5" customHeight="1">
+    <row r="188" ht="13.5" hidden="1" customHeight="1">
       <c r="A188" s="3" t="s">
         <v>193</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="189" ht="13.5" customHeight="1">
+    <row r="189" ht="13.5" hidden="1" customHeight="1">
       <c r="A189" s="3" t="s">
         <v>194</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="190" ht="13.5" customHeight="1">
+    <row r="190" ht="13.5" hidden="1" customHeight="1">
       <c r="A190" s="3" t="s">
         <v>195</v>
       </c>
@@ -9056,7 +9056,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="191" ht="13.5" customHeight="1">
+    <row r="191" ht="13.5" hidden="1" customHeight="1">
       <c r="A191" s="3" t="s">
         <v>196</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="192" ht="13.5" customHeight="1">
+    <row r="192" ht="13.5" hidden="1" customHeight="1">
       <c r="A192" s="3" t="s">
         <v>131</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="193" ht="13.5" customHeight="1">
+    <row r="193" ht="13.5" hidden="1" customHeight="1">
       <c r="A193" s="3" t="s">
         <v>197</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="194" ht="13.5" customHeight="1">
+    <row r="194" ht="13.5" hidden="1" customHeight="1">
       <c r="A194" s="3" t="s">
         <v>198</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="195" ht="13.5" customHeight="1">
+    <row r="195" ht="13.5" hidden="1" customHeight="1">
       <c r="A195" s="3" t="s">
         <v>199</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="196" ht="13.5" customHeight="1">
+    <row r="196" ht="13.5" hidden="1" customHeight="1">
       <c r="A196" s="3" t="s">
         <v>200</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="197" ht="13.5" customHeight="1">
+    <row r="197" ht="13.5" hidden="1" customHeight="1">
       <c r="A197" s="3" t="s">
         <v>201</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="198" ht="13.5" customHeight="1">
+    <row r="198" ht="13.5" hidden="1" customHeight="1">
       <c r="A198" s="3" t="s">
         <v>202</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="199" ht="13.5" customHeight="1">
+    <row r="199" ht="13.5" hidden="1" customHeight="1">
       <c r="A199" s="3" t="s">
         <v>203</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="200" ht="13.5" customHeight="1">
+    <row r="200" ht="13.5" hidden="1" customHeight="1">
       <c r="A200" s="3" t="s">
         <v>204</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="201" ht="13.5" customHeight="1">
+    <row r="201" ht="13.5" hidden="1" customHeight="1">
       <c r="A201" s="3" t="s">
         <v>205</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="202" ht="13.5" customHeight="1">
+    <row r="202" ht="13.5" hidden="1" customHeight="1">
       <c r="A202" s="3" t="s">
         <v>206</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="203" ht="13.5" customHeight="1">
+    <row r="203" ht="13.5" hidden="1" customHeight="1">
       <c r="A203" s="3" t="s">
         <v>207</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="204" ht="13.5" customHeight="1">
+    <row r="204" ht="13.5" hidden="1" customHeight="1">
       <c r="A204" s="3" t="s">
         <v>208</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="205" ht="13.5" customHeight="1">
+    <row r="205" ht="13.5" hidden="1" customHeight="1">
       <c r="A205" s="3" t="s">
         <v>209</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="207" ht="13.5" customHeight="1">
+    <row r="207" ht="13.5" hidden="1" customHeight="1">
       <c r="A207" s="3" t="s">
         <v>125</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="208" ht="13.5" customHeight="1">
+    <row r="208" ht="13.5" hidden="1" customHeight="1">
       <c r="A208" s="3" t="s">
         <v>211</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="209" ht="13.5" customHeight="1">
+    <row r="209" ht="13.5" hidden="1" customHeight="1">
       <c r="A209" s="3" t="s">
         <v>212</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="210" ht="13.5" customHeight="1">
+    <row r="210" ht="13.5" hidden="1" customHeight="1">
       <c r="A210" s="3" t="s">
         <v>213</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="211" ht="13.5" customHeight="1">
+    <row r="211" ht="13.5" hidden="1" customHeight="1">
       <c r="A211" s="3" t="s">
         <v>214</v>
       </c>
@@ -9917,7 +9917,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="212" ht="13.5" customHeight="1">
+    <row r="212" ht="13.5" hidden="1" customHeight="1">
       <c r="A212" s="3" t="s">
         <v>215</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="213" ht="13.5" customHeight="1">
+    <row r="213" ht="13.5" hidden="1" customHeight="1">
       <c r="A213" s="3" t="s">
         <v>216</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="214" ht="13.5" customHeight="1">
+    <row r="214" ht="13.5" hidden="1" customHeight="1">
       <c r="A214" s="3" t="s">
         <v>217</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="215" ht="13.5" customHeight="1">
+    <row r="215" ht="13.5" hidden="1" customHeight="1">
       <c r="A215" s="3" t="s">
         <v>218</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="216" ht="13.5" customHeight="1">
+    <row r="216" ht="13.5" hidden="1" customHeight="1">
       <c r="A216" s="3" t="s">
         <v>219</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="217" ht="13.5" customHeight="1">
+    <row r="217" ht="13.5" hidden="1" customHeight="1">
       <c r="A217" s="3" t="s">
         <v>220</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="218" ht="13.5" customHeight="1">
+    <row r="218" ht="13.5" hidden="1" customHeight="1">
       <c r="A218" s="3" t="s">
         <v>221</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="219" ht="13.5" customHeight="1">
+    <row r="219" ht="13.5" hidden="1" customHeight="1">
       <c r="A219" s="3" t="s">
         <v>222</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="220" ht="13.5" customHeight="1">
+    <row r="220" ht="13.5" hidden="1" customHeight="1">
       <c r="A220" s="3" t="s">
         <v>223</v>
       </c>
@@ -10286,7 +10286,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="221" ht="13.5" customHeight="1">
+    <row r="221" ht="13.5" hidden="1" customHeight="1">
       <c r="A221" s="3" t="s">
         <v>224</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="222" ht="13.5" customHeight="1">
+    <row r="222" ht="13.5" hidden="1" customHeight="1">
       <c r="A222" s="3" t="s">
         <v>225</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="223" ht="13.5" customHeight="1">
+    <row r="223" ht="13.5" hidden="1" customHeight="1">
       <c r="A223" s="3" t="s">
         <v>226</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="224" ht="13.5" customHeight="1">
+    <row r="224" ht="13.5" hidden="1" customHeight="1">
       <c r="A224" s="3" t="s">
         <v>227</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="225" ht="13.5" customHeight="1">
+    <row r="225" ht="13.5" hidden="1" customHeight="1">
       <c r="A225" s="3" t="s">
         <v>228</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="226" ht="13.5" customHeight="1">
+    <row r="226" ht="13.5" hidden="1" customHeight="1">
       <c r="A226" s="3" t="s">
         <v>229</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="227" ht="13.5" customHeight="1">
+    <row r="227" ht="13.5" hidden="1" customHeight="1">
       <c r="A227" s="3" t="s">
         <v>230</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="228" ht="13.5" customHeight="1">
+    <row r="228" ht="13.5" hidden="1" customHeight="1">
       <c r="A228" s="3" t="s">
         <v>231</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="229" ht="13.5" customHeight="1">
+    <row r="229" ht="13.5" hidden="1" customHeight="1">
       <c r="A229" s="3" t="s">
         <v>232</v>
       </c>
@@ -10655,7 +10655,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="230" ht="13.5" customHeight="1">
+    <row r="230" ht="13.5" hidden="1" customHeight="1">
       <c r="A230" s="3" t="s">
         <v>233</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="231" ht="13.5" customHeight="1">
+    <row r="231" ht="13.5" hidden="1" customHeight="1">
       <c r="A231" s="3" t="s">
         <v>234</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="232" ht="13.5" customHeight="1">
+    <row r="232" ht="13.5" hidden="1" customHeight="1">
       <c r="A232" s="3" t="s">
         <v>235</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="233" ht="13.5" customHeight="1">
+    <row r="233" ht="13.5" hidden="1" customHeight="1">
       <c r="A233" s="3" t="s">
         <v>236</v>
       </c>
@@ -10950,7 +10950,13 @@
       <c r="H273"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M233"/>
+  <autoFilter ref="A1:M233">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="22322"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
